--- a/output/country_population.xlsx
+++ b/output/country_population.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1865,6 +1865,1406 @@
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Iran</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Tehran</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>85961000</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Southern Asia</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Jakarta</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>284438782</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>South-Eastern Asia</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Timor-Leste</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Dili</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>1391221</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>South-Eastern Asia</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Turkmenistan</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ashgabat</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>7057841</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Central Asia</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Maldives</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Malé</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>515132</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Southern Asia</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Mongolia</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ulan Bator</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>3544835</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Eastern Asia</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Cambodia</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Phnom Penh</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>17577760</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>South-Eastern Asia</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Bahrain</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Manama</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>1594654</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Western Asia</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Seoul</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>51159889</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Eastern Asia</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Jerusalem</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>10134800</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Western Asia</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>11294243</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Western Asia</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>North Korea</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Pyongyang</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>25950000</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Eastern Asia</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Turkey</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ankara</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>85664944</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Western Asia</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Armenia</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Yerevan</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>3076200</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Western Asia</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Myanmar</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Naypyidaw</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>51316756</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>South-Eastern Asia</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Amman</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>11734000</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Western Asia</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>6110200</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>South-Eastern Asia</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Yemen</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Sana'a</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>32684503</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Western Asia</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>35300280</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Western Asia</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Hanoi</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>101343800</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>South-Eastern Asia</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Oman</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Muscat</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>5343630</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Western Asia</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>1408280000</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Eastern Asia</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Brunei</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Bandar Seri Begawan</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>455500</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>South-Eastern Asia</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Islamabad</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>241499431</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Southern Asia</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>169828911</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Southern Asia</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Afghanistan</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Kabul</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>43844000</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Southern Asia</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>65859640</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>South-Eastern Asia</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Kazakhstan</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Astana</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>20426568</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Central Asia</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Kuala Lumpur</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>34231700</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>South-Eastern Asia</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>City of Victoria</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>7527500</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Eastern Asia</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Doha</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>3173024</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Western Asia</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Kyrgyzstan</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Bishkek</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>7281800</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Central Asia</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Macau</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>685900</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Eastern Asia</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Palestine</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Ramallah</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>5483450</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Western Asia</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Tokyo</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>123210000</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Eastern Asia</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Tbilisi</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>4000921</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Western Asia</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Kuwait</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Kuwait City</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>4881254</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Western Asia</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Syria</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Damascus</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>25620000</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Western Asia</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Azerbaijan</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Baku</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10241722</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Western Asia</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Lebanon</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Beirut</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>5490000</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Western Asia</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Nepal</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Kathmandu</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>29911840</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Southern Asia</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Laos</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Vientiane</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>7647000</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>South-Eastern Asia</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Iraq</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Baghdad</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>46118793</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Western Asia</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Taipei</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>23317031</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Eastern Asia</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>1417492000</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Southern Asia</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Sri Lanka</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Sri Jayawardenepura Kotte</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>21763170</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Southern Asia</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Tajikistan</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Dushanbe</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10499000</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Central Asia</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Manila</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>114123600</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>South-Eastern Asia</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Bhutan</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Thimphu</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>784043</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Southern Asia</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Uzbekistan</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Tashkent</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>37859698</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Central Asia</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/country_population.xlsx
+++ b/output/country_population.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F101"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -441,27 +441,32 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>capital</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>region</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>subregion</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>population</t>
         </is>
       </c>
     </row>
@@ -1860,1406 +1865,6 @@
         </is>
       </c>
       <c r="F51" t="inlineStr">
-        <is>
-          <t>Central Asia</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Iran</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Tehran</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>85961000</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Southern Asia</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Jakarta</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>284438782</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>South-Eastern Asia</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Timor-Leste</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Dili</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>1391221</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>South-Eastern Asia</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>54</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Turkmenistan</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ashgabat</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>7057841</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Central Asia</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>55</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Maldives</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Malé</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>515132</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Southern Asia</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>56</v>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Mongolia</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ulan Bator</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>3544835</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Eastern Asia</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>57</v>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Cambodia</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Phnom Penh</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>17577760</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>South-Eastern Asia</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>58</v>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Bahrain</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Manama</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>1594654</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Western Asia</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>59</v>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>South Korea</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Seoul</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>51159889</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Eastern Asia</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>60</v>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Israel</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Jerusalem</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>10134800</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Western Asia</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>61</v>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>United Arab Emirates</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Abu Dhabi</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>11294243</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Western Asia</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>62</v>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>North Korea</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Pyongyang</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>25950000</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Eastern Asia</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>63</v>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Turkey</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ankara</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>85664944</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Western Asia</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>64</v>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Armenia</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Yerevan</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>3076200</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Western Asia</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>65</v>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Myanmar</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Naypyidaw</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>51316756</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>South-Eastern Asia</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>66</v>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Jordan</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Amman</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>11734000</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Western Asia</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>67</v>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Singapore</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Singapore</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>6110200</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>South-Eastern Asia</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>68</v>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Yemen</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Sana'a</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>32684503</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Western Asia</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>69</v>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Saudi Arabia</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Riyadh</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>35300280</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Western Asia</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>70</v>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Vietnam</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Hanoi</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>101343800</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>South-Eastern Asia</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>71</v>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Oman</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Muscat</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>5343630</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Western Asia</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>72</v>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Beijing</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>1408280000</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Eastern Asia</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>73</v>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Brunei</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Bandar Seri Begawan</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>455500</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>South-Eastern Asia</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>74</v>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Pakistan</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Islamabad</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>241499431</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Southern Asia</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>75</v>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Bangladesh</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Dhaka</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>169828911</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Southern Asia</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="n">
-        <v>76</v>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Afghanistan</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Kabul</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>43844000</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Southern Asia</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="n">
-        <v>77</v>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Thailand</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Bangkok</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>65859640</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>South-Eastern Asia</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="n">
-        <v>78</v>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Kazakhstan</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Astana</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>20426568</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Central Asia</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="n">
-        <v>79</v>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Malaysia</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Kuala Lumpur</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>34231700</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>South-Eastern Asia</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
-        <v>80</v>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Hong Kong</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>City of Victoria</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>7527500</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Eastern Asia</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="n">
-        <v>81</v>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Doha</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>3173024</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Western Asia</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="n">
-        <v>82</v>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Kyrgyzstan</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Bishkek</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>7281800</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Central Asia</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="n">
-        <v>83</v>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Macau</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>685900</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Eastern Asia</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="n">
-        <v>84</v>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Palestine</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Ramallah</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>5483450</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Western Asia</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="n">
-        <v>85</v>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Tokyo</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>123210000</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Eastern Asia</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="n">
-        <v>86</v>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Georgia</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Tbilisi</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>4000921</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Western Asia</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="n">
-        <v>87</v>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Kuwait</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Kuwait City</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>4881254</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>Western Asia</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="n">
-        <v>88</v>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Syria</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Damascus</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>25620000</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Western Asia</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="n">
-        <v>89</v>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Azerbaijan</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Baku</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10241722</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Western Asia</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="n">
-        <v>90</v>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Lebanon</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Beirut</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>5490000</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Western Asia</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="n">
-        <v>91</v>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Nepal</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Kathmandu</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>29911840</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Southern Asia</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="n">
-        <v>92</v>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Laos</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Vientiane</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>7647000</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>South-Eastern Asia</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="n">
-        <v>93</v>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Iraq</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Baghdad</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>46118793</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Western Asia</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="n">
-        <v>94</v>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Taiwan</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Taipei</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>23317031</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Eastern Asia</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="n">
-        <v>95</v>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>New Delhi</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>1417492000</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Southern Asia</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="n">
-        <v>96</v>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Sri Lanka</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Sri Jayawardenepura Kotte</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>21763170</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Southern Asia</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="n">
-        <v>97</v>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Tajikistan</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Dushanbe</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10499000</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Central Asia</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="n">
-        <v>98</v>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Philippines</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Manila</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>114123600</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>South-Eastern Asia</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="n">
-        <v>99</v>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Bhutan</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Thimphu</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>784043</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>Southern Asia</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="n">
-        <v>100</v>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Uzbekistan</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Tashkent</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>37859698</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
         <is>
           <t>Central Asia</t>
         </is>
